--- a/docs/Logic Requirements/Ageipelago Sforza.xlsx
+++ b/docs/Logic Requirements/Ageipelago Sforza.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/Logic Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{8D1B09DB-DBDB-4DD1-BC63-4C91C69B709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4945CDF6-862E-4812-849B-71DF06044A34}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79F1221-5F41-45A5-B574-245350B5281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sforza" sheetId="1" r:id="rId1"/>
+    <sheet name="Mercenaries and Masters" sheetId="2" r:id="rId2"/>
+    <sheet name="His own Man" sheetId="7" r:id="rId3"/>
+    <sheet name="Prodigal Son" sheetId="8" r:id="rId4"/>
+    <sheet name="Blood and Betrayal" sheetId="9" r:id="rId5"/>
+    <sheet name="Viva Sforza!" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="168">
   <si>
     <t>Scenario</t>
   </si>
@@ -457,96 +462,6 @@
 20 Condottieri
 16 Cavalier
 16 Hand Cannoneers</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-12 Condottieri
-8 Hand Cannoneers
-9 Cavalier
-1 Monk
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-21 Condottieri
-15 Chavalier
-15 Hand Cannoneers
-1 Monk
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-14 Condottieri
-10 Chavalier
-10 Hand Cannoneers
-1 Monk
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-28 Condottieri
-20 Chavalier
-20 Hand Cannoneers
-1 Monk</t>
     </r>
   </si>
   <si>
@@ -1340,10 +1255,6 @@
 500 Stone</t>
   </si>
   <si>
-    <t>Starting Units:
-1 Hunting Wold</t>
-  </si>
-  <si>
     <t>Reach Cremona</t>
   </si>
   <si>
@@ -1811,16 +1722,6 @@
 Bombard Cannons</t>
   </si>
   <si>
-    <t>Starting Units:
-19 Condottieri
-4 Genoese Crossbowmen
-2 Knights
-Later:
-Skirmishers, Pikemen, Light Cavalry, War Galleys, Fire Ships and Demolition Ships reactive as Counterunits
-Condottieri, Cavaliers, Hand Cannoneers, Genoese Crossbowmen and Scorpions as Main Force.
-Bombard Cannons</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Starting Units:
 8 Condottieri
@@ -1997,12 +1898,441 @@
 Once again, an enemy has Reactive AI.
 There's SOMETHING reactive in Players 3 and 4, maybe total Army size?</t>
   </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Condottiero</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer</t>
+  </si>
+  <si>
+    <t>Genoese Crossbowman</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+12 Condottieri
+8 Hand Cannoneers
+9 Cavalier
+1 Monk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+21 Condottieri
+15 Cavalier
+15 Hand Cannoneers
+1 Monk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+14 Condottieri
+10 Cavalier
+10 Hand Cannoneers
+1 Monk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+28 Condottieri
+20 Cavalier
+20 Hand Cannoneers
+1 Monk</t>
+    </r>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Donkey</t>
+  </si>
+  <si>
+    <t>Ibex</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>Hunting Wolf</t>
+  </si>
+  <si>
+    <t>Only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Aqueduct</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Barricade</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>No Trade Cart
+No Villagers
+No Naval Units
+No Castle Units</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>No Castle Techs
+No Dock Techs
+No Crop Rotation
+University Techs only on Hard Logic</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Siege Workshop
+Farms can be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>re</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>built</t>
+    </r>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Feudal - Imperial Age</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Bombard Tower</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Sea Gate</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>Converts to Player</t>
+  </si>
+  <si>
+    <t>No Fishing Ship
+No Trade Cog
+No Trade Cart
+No Villager</t>
+  </si>
+  <si>
+    <t>No Silk Road
+No Spies
+No Eco Techs except Guilds</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Cow</t>
+  </si>
+  <si>
+    <t>Goose</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Elite Genoese Crossbowman</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Demolition Ship</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Spies</t>
+  </si>
+  <si>
+    <t>Pig</t>
+  </si>
+  <si>
+    <t>No Wonder</t>
+  </si>
+  <si>
+    <t>Starting Units:
+1 Hunting Wolf</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Fishing Boat</t>
+  </si>
+  <si>
+    <t>Organ Cannon</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Trade Cog</t>
+  </si>
+  <si>
+    <t>Elite Organ Cannon</t>
+  </si>
+  <si>
+    <t>Feitoria</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Starting Units:
+19 Condottieri
+4 Genoese Crossbowmen
+2 Knights
+Later:
+Skirmishers, Pikemen and Light Cavalry reactive as Counterunits
+Condottieri, Cavaliers, Hand Cannoneers, Genoese Crossbowmen and Scorpions as Main Force.
+Bombard Cannons</t>
+  </si>
+  <si>
+    <t>Elite Organ Connan</t>
+  </si>
+  <si>
+    <t>Sigismondo Malatesta</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2115,6 +2445,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2FE2F5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2124,7 +2501,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2212,11 +2589,105 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2252,6 +2723,124 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2661,10 +3250,10 @@
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>21</v>
@@ -2677,38 +3266,38 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>36</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>37</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -2719,27 +3308,27 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>46</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -2747,7 +3336,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2755,41 +3344,41 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2797,41 +3386,41 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="F8" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="I8" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>66</v>
+        <v>164</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2856,4 +3445,2838 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A9EFA2C-2A03-49A0-869D-B102BF86A8A8}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="G2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="K28" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D49308-974C-4DDB-B253-11817D5B5178}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="G2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="K28" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="K29" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="K30" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBBD65B-FB65-4A10-9F1F-7DB7B0A6756C}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="G2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="K28" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="L28" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6866A1-7115-4C86-8491-5103B4C08E12}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="G2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="L23" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D04B0B3-1D4C-4652-942C-32FD5AE05208}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="G2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="K28" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="L28" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="15"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Sforza.xlsx
+++ b/docs/Logic Requirements/Ageipelago Sforza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79F1221-5F41-45A5-B574-245350B5281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF97706-CB7B-4A34-B078-240A8C2E4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sforza" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="169">
   <si>
     <t>Scenario</t>
   </si>
@@ -2154,12 +2154,6 @@
     <t>Guard Tower</t>
   </si>
   <si>
-    <t>No Castle Techs
-No Dock Techs
-No Crop Rotation
-University Techs only on Hard Logic</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Siege Workshop
 Farms can be </t>
@@ -2326,6 +2320,20 @@
   </si>
   <si>
     <t>Paladin</t>
+  </si>
+  <si>
+    <t>No Castle Techs
+No Dock Techs
+No Crop Rotation
+University Techs only on Hard Logic
+Chemistry is researched automatically
+On Standard:
+Conscription is researched automatically</t>
+  </si>
+  <si>
+    <t>No Spies
+On Standard:
+Light Cavalry and Crossbowman are researched automatically</t>
   </si>
 </sst>
 </file>
@@ -2789,24 +2797,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2841,6 +2831,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3373,7 +3381,7 @@
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
@@ -3407,7 +3415,7 @@
         <v>66</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>65</v>
@@ -3459,11 +3467,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
         <v>72</v>
       </c>
@@ -3478,11 +3486,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
         <v>85</v>
       </c>
@@ -3523,18 +3531,18 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>120</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>67</v>
@@ -3774,7 +3782,7 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="48" t="s">
+      <c r="G18" s="42" t="s">
         <v>88</v>
       </c>
       <c r="H18" s="21" t="s">
@@ -3790,7 +3798,7 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="49" t="s">
+      <c r="G19" s="43" t="s">
         <v>89</v>
       </c>
       <c r="H19" s="21" t="s">
@@ -3806,7 +3814,7 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="44" t="s">
         <v>92</v>
       </c>
       <c r="H20" s="16" t="s">
@@ -4021,11 +4029,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
         <v>72</v>
       </c>
@@ -4040,11 +4048,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
         <v>85</v>
       </c>
@@ -4053,7 +4061,7 @@
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="36" t="s">
         <v>104</v>
       </c>
       <c r="L3" s="21" t="s">
@@ -4074,7 +4082,7 @@
         <v>82</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
@@ -4087,19 +4095,19 @@
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>138</v>
-      </c>
       <c r="G5" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
@@ -4118,7 +4126,7 @@
         <v>83</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -4137,7 +4145,7 @@
         <v>84</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
@@ -4153,15 +4161,15 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L8" s="21" t="s">
         <v>67</v>
@@ -4175,7 +4183,7 @@
         <v>119</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -4209,7 +4217,7 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="35" t="s">
         <v>76</v>
       </c>
       <c r="H11" s="23" t="s">
@@ -4247,8 +4255,8 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="G13" s="41" t="s">
-        <v>126</v>
+      <c r="G13" s="35" t="s">
+        <v>125</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>67</v>
@@ -4349,7 +4357,7 @@
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L20" s="21" t="s">
         <v>67</v>
@@ -4361,7 +4369,7 @@
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>67</v>
@@ -4397,7 +4405,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L24" s="21" t="s">
         <v>67</v>
@@ -4408,7 +4416,7 @@
       <c r="H25" s="34"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
-      <c r="K25" s="43" t="s">
+      <c r="K25" s="37" t="s">
         <v>113</v>
       </c>
       <c r="L25" s="21" t="s">
@@ -4420,7 +4428,7 @@
       <c r="H26" s="34"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
-      <c r="K26" s="43" t="s">
+      <c r="K26" s="37" t="s">
         <v>117</v>
       </c>
       <c r="L26" s="21" t="s">
@@ -4442,31 +4450,31 @@
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
-      <c r="K28" s="51" t="s">
-        <v>133</v>
+      <c r="K28" s="45" t="s">
+        <v>132</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
-      <c r="K29" s="51" t="s">
-        <v>134</v>
+      <c r="K29" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="L30" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4563,11 +4571,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
         <v>72</v>
       </c>
@@ -4582,11 +4590,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
         <v>85</v>
       </c>
@@ -4595,7 +4603,7 @@
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
-      <c r="K3" s="44" t="s">
+      <c r="K3" s="38" t="s">
         <v>94</v>
       </c>
       <c r="L3" s="21" t="s">
@@ -4627,18 +4635,18 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>74</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>67</v>
@@ -4675,8 +4683,8 @@
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
-      <c r="G7" s="47" t="s">
-        <v>140</v>
+      <c r="G7" s="41" t="s">
+        <v>139</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>67</v>
@@ -4694,8 +4702,8 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
-      <c r="G8" s="47" t="s">
-        <v>141</v>
+      <c r="G8" s="41" t="s">
+        <v>140</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>67</v>
@@ -4714,7 +4722,7 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>67</v>
@@ -4779,7 +4787,7 @@
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L12" s="21" t="s">
         <v>67</v>
@@ -4790,7 +4798,7 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>67</v>
@@ -4798,7 +4806,7 @@
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>67</v>
@@ -4847,7 +4855,7 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>67</v>
@@ -4879,7 +4887,7 @@
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G18" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>67</v>
@@ -4887,7 +4895,7 @@
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L18" s="21" t="s">
         <v>67</v>
@@ -4895,7 +4903,7 @@
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>67</v>
@@ -4911,7 +4919,7 @@
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>67</v>
@@ -4927,7 +4935,7 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>67</v>
@@ -4943,7 +4951,7 @@
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H22" s="21" t="s">
         <v>67</v>
@@ -4951,15 +4959,15 @@
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L22" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="41" t="s">
-        <v>147</v>
+      <c r="G23" s="35" t="s">
+        <v>146</v>
       </c>
       <c r="H23" s="23" t="s">
         <v>67</v>
@@ -4967,7 +4975,7 @@
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L23" s="21" t="s">
         <v>67</v>
@@ -4990,7 +4998,7 @@
       <c r="H25" s="34"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
-      <c r="K25" s="43" t="s">
+      <c r="K25" s="37" t="s">
         <v>112</v>
       </c>
       <c r="L25" s="21" t="s">
@@ -5002,7 +5010,7 @@
       <c r="H26" s="34"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
-      <c r="K26" s="43" t="s">
+      <c r="K26" s="37" t="s">
         <v>99</v>
       </c>
       <c r="L26" s="21" t="s">
@@ -5024,7 +5032,7 @@
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
-      <c r="K28" s="41" t="s">
+      <c r="K28" s="35" t="s">
         <v>117</v>
       </c>
       <c r="L28" s="23" t="s">
@@ -5137,11 +5145,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
         <v>72</v>
       </c>
@@ -5156,11 +5164,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
         <v>85</v>
       </c>
@@ -5169,7 +5177,7 @@
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="36" t="s">
         <v>118</v>
       </c>
       <c r="L3" s="21" t="s">
@@ -5187,7 +5195,7 @@
         <v>68</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>67</v>
@@ -5203,16 +5211,16 @@
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>74</v>
       </c>
       <c r="D5" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>150</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>151</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>67</v>
@@ -5220,7 +5228,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L5" s="21" t="s">
         <v>67</v>
@@ -5231,7 +5239,7 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>67</v>
@@ -5239,7 +5247,7 @@
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L6" s="21" t="s">
         <v>67</v>
@@ -5249,8 +5257,8 @@
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
-      <c r="G7" s="50" t="s">
-        <v>154</v>
+      <c r="G7" s="44" t="s">
+        <v>153</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>67</v>
@@ -5269,7 +5277,7 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>67</v>
@@ -5296,7 +5304,7 @@
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L9" s="21" t="s">
         <v>67</v>
@@ -5307,7 +5315,7 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>67</v>
@@ -5326,7 +5334,7 @@
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
       <c r="G11" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>67</v>
@@ -5364,7 +5372,7 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>67</v>
@@ -5372,7 +5380,7 @@
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>67</v>
@@ -5402,7 +5410,7 @@
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
       <c r="G15" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>67</v>
@@ -5421,7 +5429,7 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>67</v>
@@ -5469,7 +5477,7 @@
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G19" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>67</v>
@@ -5485,7 +5493,7 @@
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>67</v>
@@ -5540,8 +5548,8 @@
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
-      <c r="K23" s="45" t="s">
-        <v>161</v>
+      <c r="K23" s="39" t="s">
+        <v>160</v>
       </c>
       <c r="L23" s="23" t="s">
         <v>67</v>
@@ -5549,7 +5557,7 @@
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>67</v>
@@ -5561,7 +5569,7 @@
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H25" s="21" t="s">
         <v>67</v>
@@ -5572,8 +5580,8 @@
       <c r="L25" s="34"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="52" t="s">
-        <v>159</v>
+      <c r="G26" s="46" t="s">
+        <v>158</v>
       </c>
       <c r="H26" s="23" t="s">
         <v>67</v>
@@ -5585,7 +5593,7 @@
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>67</v>
@@ -5597,7 +5605,7 @@
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>67</v>
@@ -5711,11 +5719,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
         <v>72</v>
       </c>
@@ -5730,11 +5738,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
         <v>85</v>
       </c>
@@ -5743,7 +5751,7 @@
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
-      <c r="K3" s="44" t="s">
+      <c r="K3" s="38" t="s">
         <v>121</v>
       </c>
       <c r="L3" s="21" t="s">
@@ -5777,7 +5785,7 @@
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>74</v>
@@ -5786,7 +5794,7 @@
         <v>74</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>67</v>
@@ -5824,7 +5832,7 @@
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>67</v>
@@ -5832,7 +5840,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>67</v>
@@ -5862,7 +5870,7 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>67</v>
@@ -5908,7 +5916,7 @@
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L11" s="21" t="s">
         <v>67</v>
@@ -5919,7 +5927,7 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>67</v>
@@ -5937,8 +5945,8 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="G13" s="50" t="s">
-        <v>167</v>
+      <c r="G13" s="44" t="s">
+        <v>166</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>67</v>
@@ -5995,7 +6003,7 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>67</v>
@@ -6027,7 +6035,7 @@
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G18" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>67</v>
@@ -6075,7 +6083,7 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>67</v>
@@ -6083,7 +6091,7 @@
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>67</v>
@@ -6091,7 +6099,7 @@
     </row>
     <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H22" s="21" t="s">
         <v>67</v>
@@ -6107,7 +6115,7 @@
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>67</v>
@@ -6123,23 +6131,23 @@
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>67</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="43" t="s">
-        <v>148</v>
+      <c r="K24" s="37" t="s">
+        <v>147</v>
       </c>
       <c r="L24" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G25" s="51" t="s">
-        <v>166</v>
+      <c r="G25" s="45" t="s">
+        <v>165</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>67</v>
@@ -6180,8 +6188,8 @@
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
-      <c r="K28" s="45" t="s">
-        <v>161</v>
+      <c r="K28" s="39" t="s">
+        <v>160</v>
       </c>
       <c r="L28" s="23" t="s">
         <v>67</v>
@@ -6190,7 +6198,7 @@
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
-      <c r="K29" s="46"/>
+      <c r="K29" s="40"/>
       <c r="L29" s="15"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">

--- a/docs/Logic Requirements/Ageipelago Sforza.xlsx
+++ b/docs/Logic Requirements/Ageipelago Sforza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF97706-CB7B-4A34-B078-240A8C2E4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF4603B-26E9-478A-8EA2-05B7B2EDD340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sforza" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="171">
   <si>
     <t>Scenario</t>
   </si>
@@ -1702,18 +1702,6 @@
   </si>
   <si>
     <t>Starting Units:
-3 Long Swordsmen
-5 Crossbowmen
-2 Genoese Crossbowmen
-2 Light Cavalry
-2 War Galleys
-Later:
-Skirmishers, Pikemen, War Galleys, Fire Ships and Demolition Ships reactive as Counterunits
-Two-Handed Swordsmen, Light Cavalry, Arbalesters and Genoese Crossbowmen as Main Force.
-Bombard Cannons</t>
-  </si>
-  <si>
-    <t>Starting Units:
 6 Condottieri
 2 Light Cavalry
 Later:
@@ -2334,6 +2322,24 @@
     <t>No Spies
 On Standard:
 Light Cavalry and Crossbowman are researched automatically</t>
+  </si>
+  <si>
+    <t>Carrack</t>
+  </si>
+  <si>
+    <t>War Hulk</t>
+  </si>
+  <si>
+    <t>Starting Units:
+3 Long Swordsmen
+5 Crossbowmen
+2 Genoese Crossbowmen
+2 Light Cavalry
+2 War Galleys
+Later:
+Skirmishers, Pikemen, War Galleys, Fire Ships and War Hulks reactive as Counterunits
+Two-Handed Swordsmen, Light Cavalry, Arbalesters and Genoese Crossbowmen as Main Force.
+Bombard Cannons</t>
   </si>
 </sst>
 </file>
@@ -3258,7 +3264,7 @@
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>29</v>
@@ -3347,7 +3353,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="357" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
@@ -3374,14 +3380,14 @@
         <v>61</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
@@ -3412,16 +3418,16 @@
         <v>60</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -3468,18 +3474,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -3487,73 +3493,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3561,18 +3567,18 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3580,18 +3586,18 @@
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3599,18 +3605,18 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -3618,18 +3624,18 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3637,18 +3643,18 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3656,18 +3662,18 @@
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
       <c r="G11" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -3675,18 +3681,18 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3694,18 +3700,18 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3713,18 +3719,18 @@
       <c r="C14" s="14"/>
       <c r="D14" s="13"/>
       <c r="G14" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3732,18 +3738,18 @@
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
       <c r="G15" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3751,82 +3757,82 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G17" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G18" s="42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3835,10 +3841,10 @@
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3847,10 +3853,10 @@
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3859,10 +3865,10 @@
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3871,10 +3877,10 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3883,10 +3889,10 @@
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3895,10 +3901,10 @@
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3907,20 +3913,20 @@
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4030,18 +4036,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -4049,73 +4055,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>137</v>
-      </c>
       <c r="G5" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4123,18 +4129,18 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4142,18 +4148,18 @@
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4161,18 +4167,18 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4180,18 +4186,18 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4199,18 +4205,18 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4218,18 +4224,18 @@
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
       <c r="G11" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4237,18 +4243,18 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4256,18 +4262,18 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4279,10 +4285,10 @@
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4294,10 +4300,10 @@
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4309,10 +4315,10 @@
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4321,10 +4327,10 @@
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4333,10 +4339,10 @@
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4345,10 +4351,10 @@
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4357,10 +4363,10 @@
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4369,10 +4375,10 @@
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4381,10 +4387,10 @@
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4393,10 +4399,10 @@
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4405,10 +4411,10 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4417,10 +4423,10 @@
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4429,10 +4435,10 @@
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4441,40 +4447,40 @@
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
       <c r="K29" s="45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="L30" s="16" t="s">
         <v>134</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4572,18 +4578,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -4591,73 +4597,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4665,18 +4671,18 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4684,18 +4690,18 @@
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4703,18 +4709,18 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4722,18 +4728,18 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4741,18 +4747,18 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4760,18 +4766,18 @@
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
       <c r="G11" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4779,18 +4785,18 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4798,18 +4804,18 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4817,18 +4823,18 @@
       <c r="C14" s="14"/>
       <c r="D14" s="13"/>
       <c r="G14" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4836,18 +4842,18 @@
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
       <c r="G15" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -4855,130 +4861,130 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G17" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G18" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4987,10 +4993,10 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4999,10 +5005,10 @@
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5011,10 +5017,10 @@
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5023,20 +5029,20 @@
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5146,18 +5152,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -5165,73 +5171,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>150</v>
-      </c>
       <c r="H5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5239,18 +5245,18 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5258,18 +5264,18 @@
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5277,18 +5283,18 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -5296,18 +5302,18 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5315,18 +5321,18 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5334,18 +5340,18 @@
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
       <c r="G11" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5353,18 +5359,18 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5372,18 +5378,18 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5391,18 +5397,18 @@
       <c r="C14" s="14"/>
       <c r="D14" s="13"/>
       <c r="G14" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5410,18 +5416,18 @@
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
       <c r="G15" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5429,138 +5435,138 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="30" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G17" s="30" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G18" s="30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="30" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G20" s="30" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="25" t="s">
-        <v>75</v>
+      <c r="G21" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="25" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="24" t="s">
-        <v>156</v>
+      <c r="G24" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
@@ -5568,11 +5574,11 @@
       <c r="L24" s="15"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="29" t="s">
-        <v>157</v>
+      <c r="G25" s="24" t="s">
+        <v>155</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
@@ -5580,11 +5586,11 @@
       <c r="L25" s="34"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>67</v>
+      <c r="G26" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
@@ -5592,11 +5598,11 @@
       <c r="L26" s="34"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>67</v>
+      <c r="G27" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>66</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
@@ -5605,17 +5611,21 @@
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>67</v>
+        <v>158</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
+      <c r="G29" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>66</v>
+      </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
     </row>
@@ -5720,18 +5730,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -5739,73 +5749,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5813,18 +5823,18 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5832,18 +5842,18 @@
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5851,18 +5861,18 @@
       <c r="C8" s="14"/>
       <c r="D8" s="13"/>
       <c r="G8" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5870,18 +5880,18 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5889,18 +5899,18 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5908,18 +5918,18 @@
       <c r="C11" s="14"/>
       <c r="D11" s="13"/>
       <c r="G11" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5927,18 +5937,18 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5946,18 +5956,18 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5965,18 +5975,18 @@
       <c r="C14" s="14"/>
       <c r="D14" s="13"/>
       <c r="G14" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -5984,18 +5994,18 @@
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
       <c r="G15" s="31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6003,162 +6013,162 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G17" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G18" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6167,10 +6177,10 @@
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6179,20 +6189,20 @@
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
